--- a/templates/ERC000052/metadata_template_ERC000052.xlsx
+++ b/templates/ERC000052/metadata_template_ERC000052.xlsx
@@ -20,7 +20,7 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$Q$1:$Q$289</definedName>
     <definedName name="hostsex">'cv_sample'!$Y$1:$Y$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="631">
   <si>
     <t>alias</t>
   </si>
@@ -556,6 +556,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -719,6 +722,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2448,7 +2454,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2492,7 +2498,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2519,7 +2525,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3238,6 +3244,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3259,27 +3275,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3299,122 +3315,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3438,228 +3454,228 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:38" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -3682,127 +3698,127 @@
   <sheetData>
     <row r="1" spans="17:25">
       <c r="Q1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Y1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="17:25">
       <c r="Q2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="17:25">
       <c r="Q3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Y3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="17:25">
       <c r="Q4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Y4" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" spans="17:25">
       <c r="Q5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Y5" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" spans="17:25">
       <c r="Q6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Y6" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" spans="17:25">
       <c r="Q7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Y7" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="17:25">
       <c r="Q8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Y8" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" spans="17:25">
       <c r="Q9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y9" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="17:25">
       <c r="Q10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Y10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" spans="17:25">
       <c r="Q11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Y11" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" spans="17:25">
       <c r="Q12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Y12" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="17:25">
       <c r="Q13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Y13" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="17:25">
       <c r="Q14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Y14" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="15" spans="17:25">
       <c r="Q15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Y15" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" spans="17:25">
       <c r="Q16" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Y16" t="s">
         <v>116</v>
@@ -3810,1370 +3826,1370 @@
     </row>
     <row r="17" spans="17:25">
       <c r="Q17" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Y17" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="18" spans="17:25">
       <c r="Q18" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="17:25">
       <c r="Q19" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="17:25">
       <c r="Q20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="17:25">
       <c r="Q21" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="17:25">
       <c r="Q22" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="17:25">
       <c r="Q23" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="17:25">
       <c r="Q24" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="17:25">
       <c r="Q25" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="17:25">
       <c r="Q26" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="17:25">
       <c r="Q27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="17:25">
       <c r="Q28" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" spans="17:25">
       <c r="Q29" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="17:25">
       <c r="Q30" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="17:25">
       <c r="Q31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="17:25">
       <c r="Q32" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="17:17">
       <c r="Q33" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="17:17">
       <c r="Q34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="17:17">
       <c r="Q35" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="17:17">
       <c r="Q36" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="17:17">
       <c r="Q37" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38" spans="17:17">
       <c r="Q38" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" spans="17:17">
       <c r="Q39" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="17:17">
       <c r="Q40" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="17:17">
       <c r="Q41" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="17:17">
       <c r="Q42" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="17:17">
       <c r="Q43" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="17:17">
       <c r="Q44" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="17:17">
       <c r="Q45" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="17:17">
       <c r="Q46" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="17:17">
       <c r="Q47" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="17:17">
       <c r="Q48" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="17:17">
       <c r="Q49" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="17:17">
       <c r="Q50" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="51" spans="17:17">
       <c r="Q51" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="17:17">
       <c r="Q52" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="17:17">
       <c r="Q53" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="17:17">
       <c r="Q54" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="17:17">
       <c r="Q55" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="17:17">
       <c r="Q56" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="57" spans="17:17">
       <c r="Q57" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="58" spans="17:17">
       <c r="Q58" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="17:17">
       <c r="Q59" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="60" spans="17:17">
       <c r="Q60" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="17:17">
       <c r="Q61" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="17:17">
       <c r="Q62" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="63" spans="17:17">
       <c r="Q63" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="17:17">
       <c r="Q64" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="65" spans="17:17">
       <c r="Q65" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="66" spans="17:17">
       <c r="Q66" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="67" spans="17:17">
       <c r="Q67" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="17:17">
       <c r="Q68" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" spans="17:17">
       <c r="Q69" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="70" spans="17:17">
       <c r="Q70" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71" spans="17:17">
       <c r="Q71" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="72" spans="17:17">
       <c r="Q72" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="73" spans="17:17">
       <c r="Q73" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="17:17">
       <c r="Q74" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="75" spans="17:17">
       <c r="Q75" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="76" spans="17:17">
       <c r="Q76" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="17:17">
       <c r="Q77" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="17:17">
       <c r="Q78" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="79" spans="17:17">
       <c r="Q79" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="80" spans="17:17">
       <c r="Q80" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="81" spans="17:17">
       <c r="Q81" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="82" spans="17:17">
       <c r="Q82" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="17:17">
       <c r="Q83" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="84" spans="17:17">
       <c r="Q84" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="85" spans="17:17">
       <c r="Q85" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="86" spans="17:17">
       <c r="Q86" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="87" spans="17:17">
       <c r="Q87" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="17:17">
       <c r="Q88" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="89" spans="17:17">
       <c r="Q89" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="90" spans="17:17">
       <c r="Q90" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="91" spans="17:17">
       <c r="Q91" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="92" spans="17:17">
       <c r="Q92" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="93" spans="17:17">
       <c r="Q93" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="94" spans="17:17">
       <c r="Q94" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="95" spans="17:17">
       <c r="Q95" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" spans="17:17">
       <c r="Q96" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="97" spans="17:17">
       <c r="Q97" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="98" spans="17:17">
       <c r="Q98" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" spans="17:17">
       <c r="Q99" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="100" spans="17:17">
       <c r="Q100" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="101" spans="17:17">
       <c r="Q101" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="17:17">
       <c r="Q102" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="103" spans="17:17">
       <c r="Q103" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="104" spans="17:17">
       <c r="Q104" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="105" spans="17:17">
       <c r="Q105" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="106" spans="17:17">
       <c r="Q106" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="107" spans="17:17">
       <c r="Q107" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108" spans="17:17">
       <c r="Q108" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="109" spans="17:17">
       <c r="Q109" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="110" spans="17:17">
       <c r="Q110" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="17:17">
       <c r="Q111" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="112" spans="17:17">
       <c r="Q112" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="113" spans="17:17">
       <c r="Q113" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114" spans="17:17">
       <c r="Q114" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="115" spans="17:17">
       <c r="Q115" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="116" spans="17:17">
       <c r="Q116" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="117" spans="17:17">
       <c r="Q117" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="118" spans="17:17">
       <c r="Q118" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="119" spans="17:17">
       <c r="Q119" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="120" spans="17:17">
       <c r="Q120" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="121" spans="17:17">
       <c r="Q121" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="122" spans="17:17">
       <c r="Q122" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="123" spans="17:17">
       <c r="Q123" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="124" spans="17:17">
       <c r="Q124" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="125" spans="17:17">
       <c r="Q125" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="126" spans="17:17">
       <c r="Q126" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="127" spans="17:17">
       <c r="Q127" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="128" spans="17:17">
       <c r="Q128" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="129" spans="17:17">
       <c r="Q129" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="130" spans="17:17">
       <c r="Q130" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="131" spans="17:17">
       <c r="Q131" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="132" spans="17:17">
       <c r="Q132" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="133" spans="17:17">
       <c r="Q133" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="134" spans="17:17">
       <c r="Q134" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="135" spans="17:17">
       <c r="Q135" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="136" spans="17:17">
       <c r="Q136" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="137" spans="17:17">
       <c r="Q137" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="138" spans="17:17">
       <c r="Q138" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="139" spans="17:17">
       <c r="Q139" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="140" spans="17:17">
       <c r="Q140" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="141" spans="17:17">
       <c r="Q141" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="142" spans="17:17">
       <c r="Q142" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="143" spans="17:17">
       <c r="Q143" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="144" spans="17:17">
       <c r="Q144" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="145" spans="17:17">
       <c r="Q145" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="146" spans="17:17">
       <c r="Q146" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="147" spans="17:17">
       <c r="Q147" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="148" spans="17:17">
       <c r="Q148" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="149" spans="17:17">
       <c r="Q149" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="150" spans="17:17">
       <c r="Q150" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="151" spans="17:17">
       <c r="Q151" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="152" spans="17:17">
       <c r="Q152" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="153" spans="17:17">
       <c r="Q153" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="154" spans="17:17">
       <c r="Q154" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="155" spans="17:17">
       <c r="Q155" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="156" spans="17:17">
       <c r="Q156" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="157" spans="17:17">
       <c r="Q157" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="158" spans="17:17">
       <c r="Q158" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="159" spans="17:17">
       <c r="Q159" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="160" spans="17:17">
       <c r="Q160" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="161" spans="17:17">
       <c r="Q161" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="162" spans="17:17">
       <c r="Q162" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="163" spans="17:17">
       <c r="Q163" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="164" spans="17:17">
       <c r="Q164" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="165" spans="17:17">
       <c r="Q165" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="166" spans="17:17">
       <c r="Q166" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="167" spans="17:17">
       <c r="Q167" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="168" spans="17:17">
       <c r="Q168" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="169" spans="17:17">
       <c r="Q169" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="170" spans="17:17">
       <c r="Q170" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="171" spans="17:17">
       <c r="Q171" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="172" spans="17:17">
       <c r="Q172" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="173" spans="17:17">
       <c r="Q173" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="174" spans="17:17">
       <c r="Q174" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="175" spans="17:17">
       <c r="Q175" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="176" spans="17:17">
       <c r="Q176" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="177" spans="17:17">
       <c r="Q177" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="178" spans="17:17">
       <c r="Q178" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="179" spans="17:17">
       <c r="Q179" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="180" spans="17:17">
       <c r="Q180" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="181" spans="17:17">
       <c r="Q181" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="182" spans="17:17">
       <c r="Q182" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="183" spans="17:17">
       <c r="Q183" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="184" spans="17:17">
       <c r="Q184" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="185" spans="17:17">
       <c r="Q185" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="186" spans="17:17">
       <c r="Q186" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="187" spans="17:17">
       <c r="Q187" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="188" spans="17:17">
       <c r="Q188" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="189" spans="17:17">
       <c r="Q189" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="190" spans="17:17">
       <c r="Q190" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="191" spans="17:17">
       <c r="Q191" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="192" spans="17:17">
       <c r="Q192" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="193" spans="17:17">
       <c r="Q193" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="194" spans="17:17">
       <c r="Q194" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="195" spans="17:17">
       <c r="Q195" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="196" spans="17:17">
       <c r="Q196" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="197" spans="17:17">
       <c r="Q197" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="198" spans="17:17">
       <c r="Q198" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="199" spans="17:17">
       <c r="Q199" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="200" spans="17:17">
       <c r="Q200" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="201" spans="17:17">
       <c r="Q201" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="202" spans="17:17">
       <c r="Q202" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="203" spans="17:17">
       <c r="Q203" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="204" spans="17:17">
       <c r="Q204" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="205" spans="17:17">
       <c r="Q205" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="206" spans="17:17">
       <c r="Q206" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="207" spans="17:17">
       <c r="Q207" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="208" spans="17:17">
       <c r="Q208" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="209" spans="17:17">
       <c r="Q209" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="210" spans="17:17">
       <c r="Q210" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="211" spans="17:17">
       <c r="Q211" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="212" spans="17:17">
       <c r="Q212" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" spans="17:17">
       <c r="Q213" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="214" spans="17:17">
       <c r="Q214" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="215" spans="17:17">
       <c r="Q215" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="216" spans="17:17">
       <c r="Q216" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="217" spans="17:17">
       <c r="Q217" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="218" spans="17:17">
       <c r="Q218" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="219" spans="17:17">
       <c r="Q219" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="220" spans="17:17">
       <c r="Q220" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="221" spans="17:17">
       <c r="Q221" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="222" spans="17:17">
       <c r="Q222" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="223" spans="17:17">
       <c r="Q223" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="224" spans="17:17">
       <c r="Q224" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="225" spans="17:17">
       <c r="Q225" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="226" spans="17:17">
       <c r="Q226" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="227" spans="17:17">
       <c r="Q227" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" spans="17:17">
       <c r="Q228" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="229" spans="17:17">
       <c r="Q229" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="230" spans="17:17">
       <c r="Q230" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="231" spans="17:17">
       <c r="Q231" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="232" spans="17:17">
       <c r="Q232" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="233" spans="17:17">
       <c r="Q233" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="234" spans="17:17">
       <c r="Q234" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="235" spans="17:17">
       <c r="Q235" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="236" spans="17:17">
       <c r="Q236" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="237" spans="17:17">
       <c r="Q237" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="238" spans="17:17">
       <c r="Q238" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="239" spans="17:17">
       <c r="Q239" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="240" spans="17:17">
       <c r="Q240" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="241" spans="17:17">
       <c r="Q241" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="242" spans="17:17">
       <c r="Q242" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="243" spans="17:17">
       <c r="Q243" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="244" spans="17:17">
       <c r="Q244" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="245" spans="17:17">
       <c r="Q245" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="246" spans="17:17">
       <c r="Q246" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="247" spans="17:17">
       <c r="Q247" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="248" spans="17:17">
       <c r="Q248" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="249" spans="17:17">
       <c r="Q249" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="250" spans="17:17">
       <c r="Q250" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="251" spans="17:17">
       <c r="Q251" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="252" spans="17:17">
       <c r="Q252" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="253" spans="17:17">
       <c r="Q253" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="254" spans="17:17">
       <c r="Q254" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="255" spans="17:17">
       <c r="Q255" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="256" spans="17:17">
       <c r="Q256" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="257" spans="17:17">
       <c r="Q257" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="258" spans="17:17">
       <c r="Q258" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="259" spans="17:17">
       <c r="Q259" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="260" spans="17:17">
       <c r="Q260" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="261" spans="17:17">
       <c r="Q261" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="262" spans="17:17">
       <c r="Q262" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="263" spans="17:17">
       <c r="Q263" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="264" spans="17:17">
       <c r="Q264" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="265" spans="17:17">
       <c r="Q265" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="266" spans="17:17">
       <c r="Q266" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="267" spans="17:17">
       <c r="Q267" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="268" spans="17:17">
       <c r="Q268" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="269" spans="17:17">
       <c r="Q269" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="270" spans="17:17">
       <c r="Q270" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="271" spans="17:17">
       <c r="Q271" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="272" spans="17:17">
       <c r="Q272" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="273" spans="17:17">
       <c r="Q273" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="274" spans="17:17">
       <c r="Q274" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="275" spans="17:17">
       <c r="Q275" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="276" spans="17:17">
       <c r="Q276" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="277" spans="17:17">
       <c r="Q277" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="278" spans="17:17">
       <c r="Q278" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="279" spans="17:17">
       <c r="Q279" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="280" spans="17:17">
       <c r="Q280" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="281" spans="17:17">
       <c r="Q281" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="282" spans="17:17">
       <c r="Q282" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="283" spans="17:17">
       <c r="Q283" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="284" spans="17:17">
       <c r="Q284" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="285" spans="17:17">
       <c r="Q285" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="286" spans="17:17">
       <c r="Q286" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="287" spans="17:17">
       <c r="Q287" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="288" spans="17:17">
       <c r="Q288" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="289" spans="17:17">
       <c r="Q289" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000052/metadata_template_ERC000052.xlsx
+++ b/templates/ERC000052/metadata_template_ERC000052.xlsx
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$Q$1:$Q$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$Q$1:$Q$294</definedName>
     <definedName name="hostsex">'cv_sample'!$Y$1:$Y$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="636">
   <si>
     <t>alias</t>
   </si>
@@ -556,6 +556,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -841,73 +844,73 @@
     <t>(Optional) Free-form text describing the sample, its origin, and its method of isolation.</t>
   </si>
   <si>
-    <t>sample storage temperature</t>
+    <t>sample_storage_temperature</t>
   </si>
   <si>
     <t>(Recommended) Temperature at which sample was stored, e.g. -80 (Units: °C)</t>
   </si>
   <si>
-    <t>sample storage buffer</t>
+    <t>sample_storage_buffer</t>
   </si>
   <si>
     <t>(Recommended) Buffer used for sample storage (e.g. rnalater)</t>
   </si>
   <si>
-    <t>sample storage device</t>
+    <t>sample_storage_device</t>
   </si>
   <si>
     <t>(Recommended) The container used to store the sample. this field accepts terms listed under container (http://purl.obolibrary.org/obo/ncit_c43186). if the proper descriptor is not listed please use text to describe the storage device.</t>
   </si>
   <si>
-    <t>sample storage location</t>
+    <t>sample_storage_location</t>
   </si>
   <si>
     <t>(Optional) Location at which sample was stored, usually name of a specific freezer/room. indicate the location name.</t>
   </si>
   <si>
-    <t>project name</t>
+    <t>project_name</t>
   </si>
   <si>
     <t>(Mandatory) Name of the project within which the sequencing was organized</t>
   </si>
   <si>
-    <t>reference host genome for decontamination</t>
+    <t>reference_host_genome_for_decontamination</t>
   </si>
   <si>
     <t>(Mandatory) Reference host genome that was mapped against for host decontamination (in the form of a valid assembly accession - e.g. in the format gca_xxxxxxx.x)</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
   </si>
   <si>
-    <t>geographic location (latitude)</t>
+    <t>geographic_location_latitude</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by latitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (longitude)</t>
+    <t>geographic_location_longitude</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by longitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
   </si>
   <si>
-    <t>trial length</t>
+    <t>trial_length</t>
   </si>
   <si>
     <t>(Recommended) Length of time from the beginning of the trial until the end of the trial (Units: years)</t>
   </si>
   <si>
-    <t>trial timepoint</t>
+    <t>trial_timepoint</t>
   </si>
   <si>
     <t>(Mandatory) Timepoint of the trial when the sample was collected - length of time after the beginning of the trial (Units: years)</t>
@@ -1126,9 +1129,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1147,6 +1147,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1348,6 +1351,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1357,9 +1363,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1399,7 +1402,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1468,6 +1471,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1543,6 +1549,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1564,6 +1573,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1609,6 +1621,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1621,6 +1636,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1630,9 +1648,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1657,6 +1672,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1717,12 +1735,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -1780,49 +1798,49 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
   </si>
   <si>
-    <t>host disease status</t>
+    <t>host_disease_status</t>
   </si>
   <si>
     <t>(Recommended) List of diseases with which the host has been diagnosed; can include multiple diagnoses. the value of the field depends on host; for humans the terms should be chosen from do (disease ontology) at http://www.disease-ontology.org, other hosts are free text</t>
   </si>
   <si>
-    <t>host common name</t>
+    <t>host_common_name</t>
   </si>
   <si>
     <t>(Mandatory) Common name of the host, e.g. human</t>
   </si>
   <si>
-    <t>host subject id</t>
+    <t>host_subject_id</t>
   </si>
   <si>
     <t>(Mandatory) A unique identifier by which each subject can be referred to, de-identified, e.g. #131</t>
   </si>
   <si>
-    <t>host taxid</t>
+    <t>host_taxid</t>
   </si>
   <si>
     <t>(Mandatory) Ncbi taxon id of the host, e.g. 9606</t>
   </si>
   <si>
-    <t>host body site</t>
+    <t>host_body_site</t>
   </si>
   <si>
     <t>(Mandatory) Name of body site where the sample was obtained from, such as a specific organ or tissue (tongue, lung etc...). for foundational model of anatomy ontology (fma) (v 3.1) terms, please see http://purl.bioontology.org/ontology/fma</t>
   </si>
   <si>
-    <t>host length</t>
-  </si>
-  <si>
-    <t>(Optional) The length of subject (Units: mm)</t>
-  </si>
-  <si>
-    <t>host total mass</t>
+    <t>host_length</t>
+  </si>
+  <si>
+    <t>(Optional) The length of subject (Units: m)</t>
+  </si>
+  <si>
+    <t>host_total_mass</t>
   </si>
   <si>
     <t>(Recommended) Total mass of the host at collection, the unit depends on host (Units: kg)</t>
@@ -1840,79 +1858,79 @@
     <t>neuter</t>
   </si>
   <si>
-    <t>host sex</t>
+    <t>host_sex</t>
   </si>
   <si>
     <t>(Optional) Gender or sex of the host.</t>
   </si>
   <si>
-    <t>host scientific name</t>
+    <t>host_scientific_name</t>
   </si>
   <si>
     <t>(Recommended) Scientific name of the natural (as opposed to laboratory) host to the organism from which sample was obtained.</t>
   </si>
   <si>
-    <t>host breed</t>
+    <t>host_breed</t>
   </si>
   <si>
     <t>(Recommended) Breed of the host (e.g. cobb-500)</t>
   </si>
   <si>
-    <t>host gutted mass</t>
+    <t>host_gutted_mass</t>
   </si>
   <si>
     <t>(Optional) Total mass of the host after gutting, the unit depends on host (Units: kg)</t>
   </si>
   <si>
-    <t>host diet</t>
+    <t>host_diet</t>
   </si>
   <si>
     <t>(Recommended) Type of diet depending on the host, for animals omnivore, herbivore etc., for humans high-fat, mediterranean etc.; can include multiple diet types</t>
   </si>
   <si>
-    <t>host diet treatment</t>
+    <t>host_diet_treatment</t>
   </si>
   <si>
     <t>(Mandatory) Experimental diet treatment/additive to normal host feed e.g. probiotic (gallipro epb5)</t>
   </si>
   <si>
-    <t>host diet treatment concentration</t>
+    <t>host_diet_treatment_concentration</t>
   </si>
   <si>
     <t>(Optional) Concentration of experimental diet treatment/additive to normal host feed as a percentage of the mass of the feed (e.g. 20%) (Units: % mass)</t>
   </si>
   <si>
-    <t>host storage container</t>
+    <t>host_storage_container</t>
   </si>
   <si>
     <t>(Optional) Storage container that the host organism is kept in before sampling (e.g. cage, water tank, pen) including details of size and type</t>
   </si>
   <si>
-    <t>host storage container pH</t>
+    <t>host_storage_container_ph</t>
   </si>
   <si>
     <t>(Optional) Ph of the medium in which the host organism is kept before sampling (e.g. ph of water in tank)</t>
   </si>
   <si>
-    <t>host storage container temperature</t>
+    <t>host_storage_container_temperature</t>
   </si>
   <si>
     <t>(Recommended) Temperature at which the host is kept before sampling (Units: °C)</t>
   </si>
   <si>
-    <t>sample volume or weight for DNA extraction</t>
-  </si>
-  <si>
-    <t>(Mandatory) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
-  </si>
-  <si>
-    <t>nucleic acid extraction</t>
+    <t>sample_volume_or_weight_for_dna_extraction</t>
+  </si>
+  <si>
+    <t>(Mandatory) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
+  </si>
+  <si>
+    <t>nucleic_acid_extraction</t>
   </si>
   <si>
     <t>(Optional) A link to a literature reference, electronic resource or a standard operating procedure (sop), that describes the material separation to recover the nucleic acid fraction from a sample</t>
   </si>
   <si>
-    <t>pcr primers</t>
+    <t>pcr_primers</t>
   </si>
   <si>
     <t>(Optional) Pcr primers that were used to amplify the sequence of the targeted gene, locus or subfragment. this field should contain all the primers used for a single pcr reaction if multiple forward or reverse primers are present in a single pcr reaction. the primer sequence should be reported in uppercase letters</t>
@@ -2451,7 +2469,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2495,7 +2513,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2522,7 +2540,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3246,6 +3264,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3267,27 +3290,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3307,122 +3330,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3446,228 +3469,228 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2" spans="1:38" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -3685,132 +3708,132 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="Q1:Y289"/>
+  <dimension ref="Q1:Y294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="17:25">
       <c r="Q1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="2" spans="17:25">
       <c r="Q2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="17:25">
       <c r="Q3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Y3" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="17:25">
       <c r="Q4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y4" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="17:25">
       <c r="Q5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y5" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="17:25">
       <c r="Q6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y6" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" spans="17:25">
       <c r="Q7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y7" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="17:25">
       <c r="Q8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y8" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" spans="17:25">
       <c r="Q9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Y9" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10" spans="17:25">
       <c r="Q10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y10" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" spans="17:25">
       <c r="Q11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Y11" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="12" spans="17:25">
       <c r="Q12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Y12" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" spans="17:25">
       <c r="Q13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Y13" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="14" spans="17:25">
       <c r="Q14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Y14" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" spans="17:25">
       <c r="Q15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y15" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16" spans="17:25">
       <c r="Q16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y16" t="s">
         <v>116</v>
@@ -3818,1370 +3841,1395 @@
     </row>
     <row r="17" spans="17:25">
       <c r="Q17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y17" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="18" spans="17:25">
       <c r="Q18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="17:25">
       <c r="Q19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="17:25">
       <c r="Q20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="17:25">
       <c r="Q21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="17:25">
       <c r="Q22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="17:25">
       <c r="Q23" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="17:25">
       <c r="Q24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="17:25">
       <c r="Q25" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="17:25">
       <c r="Q26" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="17:25">
       <c r="Q27" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="17:25">
       <c r="Q28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" spans="17:25">
       <c r="Q29" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="17:25">
       <c r="Q30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="17:25">
       <c r="Q31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="17:25">
       <c r="Q32" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="17:17">
       <c r="Q33" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="17:17">
       <c r="Q34" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="17:17">
       <c r="Q35" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="17:17">
       <c r="Q36" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="17:17">
       <c r="Q37" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38" spans="17:17">
       <c r="Q38" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" spans="17:17">
       <c r="Q39" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="17:17">
       <c r="Q40" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="17:17">
       <c r="Q41" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="17:17">
       <c r="Q42" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="17:17">
       <c r="Q43" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="17:17">
       <c r="Q44" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="17:17">
       <c r="Q45" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="17:17">
       <c r="Q46" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="17:17">
       <c r="Q47" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="17:17">
       <c r="Q48" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="17:17">
       <c r="Q49" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="17:17">
       <c r="Q50" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="51" spans="17:17">
       <c r="Q51" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="17:17">
       <c r="Q52" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="17:17">
       <c r="Q53" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="17:17">
       <c r="Q54" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="17:17">
       <c r="Q55" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="17:17">
       <c r="Q56" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="57" spans="17:17">
       <c r="Q57" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="58" spans="17:17">
       <c r="Q58" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="17:17">
       <c r="Q59" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="60" spans="17:17">
       <c r="Q60" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="17:17">
       <c r="Q61" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="17:17">
       <c r="Q62" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="63" spans="17:17">
       <c r="Q63" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="17:17">
       <c r="Q64" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="65" spans="17:17">
       <c r="Q65" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="66" spans="17:17">
       <c r="Q66" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="67" spans="17:17">
       <c r="Q67" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="17:17">
       <c r="Q68" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" spans="17:17">
       <c r="Q69" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="70" spans="17:17">
       <c r="Q70" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71" spans="17:17">
       <c r="Q71" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="72" spans="17:17">
       <c r="Q72" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="73" spans="17:17">
       <c r="Q73" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="17:17">
       <c r="Q74" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="75" spans="17:17">
       <c r="Q75" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="76" spans="17:17">
       <c r="Q76" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="17:17">
       <c r="Q77" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="17:17">
       <c r="Q78" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="79" spans="17:17">
       <c r="Q79" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="80" spans="17:17">
       <c r="Q80" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="81" spans="17:17">
       <c r="Q81" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="82" spans="17:17">
       <c r="Q82" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="17:17">
       <c r="Q83" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="84" spans="17:17">
       <c r="Q84" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="85" spans="17:17">
       <c r="Q85" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="86" spans="17:17">
       <c r="Q86" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="87" spans="17:17">
       <c r="Q87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="17:17">
       <c r="Q88" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="89" spans="17:17">
       <c r="Q89" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="90" spans="17:17">
       <c r="Q90" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="91" spans="17:17">
       <c r="Q91" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="92" spans="17:17">
       <c r="Q92" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="93" spans="17:17">
       <c r="Q93" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="94" spans="17:17">
       <c r="Q94" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="95" spans="17:17">
       <c r="Q95" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" spans="17:17">
       <c r="Q96" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="97" spans="17:17">
       <c r="Q97" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="98" spans="17:17">
       <c r="Q98" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" spans="17:17">
       <c r="Q99" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="100" spans="17:17">
       <c r="Q100" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="101" spans="17:17">
       <c r="Q101" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="17:17">
       <c r="Q102" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="103" spans="17:17">
       <c r="Q103" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="104" spans="17:17">
       <c r="Q104" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="105" spans="17:17">
       <c r="Q105" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="106" spans="17:17">
       <c r="Q106" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="107" spans="17:17">
       <c r="Q107" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108" spans="17:17">
       <c r="Q108" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="109" spans="17:17">
       <c r="Q109" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="110" spans="17:17">
       <c r="Q110" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="17:17">
       <c r="Q111" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="112" spans="17:17">
       <c r="Q112" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="113" spans="17:17">
       <c r="Q113" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114" spans="17:17">
       <c r="Q114" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="115" spans="17:17">
       <c r="Q115" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="116" spans="17:17">
       <c r="Q116" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="117" spans="17:17">
       <c r="Q117" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="118" spans="17:17">
       <c r="Q118" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="119" spans="17:17">
       <c r="Q119" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="120" spans="17:17">
       <c r="Q120" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="121" spans="17:17">
       <c r="Q121" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="122" spans="17:17">
       <c r="Q122" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="123" spans="17:17">
       <c r="Q123" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="124" spans="17:17">
       <c r="Q124" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="125" spans="17:17">
       <c r="Q125" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="126" spans="17:17">
       <c r="Q126" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="127" spans="17:17">
       <c r="Q127" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="128" spans="17:17">
       <c r="Q128" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="129" spans="17:17">
       <c r="Q129" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="130" spans="17:17">
       <c r="Q130" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="131" spans="17:17">
       <c r="Q131" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="132" spans="17:17">
       <c r="Q132" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="133" spans="17:17">
       <c r="Q133" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="134" spans="17:17">
       <c r="Q134" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="135" spans="17:17">
       <c r="Q135" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="136" spans="17:17">
       <c r="Q136" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="137" spans="17:17">
       <c r="Q137" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="138" spans="17:17">
       <c r="Q138" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="139" spans="17:17">
       <c r="Q139" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="140" spans="17:17">
       <c r="Q140" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="141" spans="17:17">
       <c r="Q141" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="142" spans="17:17">
       <c r="Q142" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="143" spans="17:17">
       <c r="Q143" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="144" spans="17:17">
       <c r="Q144" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="145" spans="17:17">
       <c r="Q145" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="146" spans="17:17">
       <c r="Q146" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="147" spans="17:17">
       <c r="Q147" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="148" spans="17:17">
       <c r="Q148" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="149" spans="17:17">
       <c r="Q149" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="150" spans="17:17">
       <c r="Q150" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="151" spans="17:17">
       <c r="Q151" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="152" spans="17:17">
       <c r="Q152" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="153" spans="17:17">
       <c r="Q153" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="154" spans="17:17">
       <c r="Q154" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="155" spans="17:17">
       <c r="Q155" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="156" spans="17:17">
       <c r="Q156" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="157" spans="17:17">
       <c r="Q157" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="158" spans="17:17">
       <c r="Q158" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="159" spans="17:17">
       <c r="Q159" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="160" spans="17:17">
       <c r="Q160" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="161" spans="17:17">
       <c r="Q161" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="162" spans="17:17">
       <c r="Q162" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="163" spans="17:17">
       <c r="Q163" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="164" spans="17:17">
       <c r="Q164" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="165" spans="17:17">
       <c r="Q165" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="166" spans="17:17">
       <c r="Q166" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="167" spans="17:17">
       <c r="Q167" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="168" spans="17:17">
       <c r="Q168" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="169" spans="17:17">
       <c r="Q169" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="170" spans="17:17">
       <c r="Q170" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="171" spans="17:17">
       <c r="Q171" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="172" spans="17:17">
       <c r="Q172" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="173" spans="17:17">
       <c r="Q173" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="174" spans="17:17">
       <c r="Q174" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="175" spans="17:17">
       <c r="Q175" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="176" spans="17:17">
       <c r="Q176" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="177" spans="17:17">
       <c r="Q177" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="178" spans="17:17">
       <c r="Q178" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="179" spans="17:17">
       <c r="Q179" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="180" spans="17:17">
       <c r="Q180" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="181" spans="17:17">
       <c r="Q181" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="182" spans="17:17">
       <c r="Q182" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="183" spans="17:17">
       <c r="Q183" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="184" spans="17:17">
       <c r="Q184" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="185" spans="17:17">
       <c r="Q185" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="186" spans="17:17">
       <c r="Q186" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="187" spans="17:17">
       <c r="Q187" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="188" spans="17:17">
       <c r="Q188" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="189" spans="17:17">
       <c r="Q189" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="190" spans="17:17">
       <c r="Q190" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="191" spans="17:17">
       <c r="Q191" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="192" spans="17:17">
       <c r="Q192" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="193" spans="17:17">
       <c r="Q193" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="194" spans="17:17">
       <c r="Q194" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="195" spans="17:17">
       <c r="Q195" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="196" spans="17:17">
       <c r="Q196" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="197" spans="17:17">
       <c r="Q197" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="198" spans="17:17">
       <c r="Q198" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="199" spans="17:17">
       <c r="Q199" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="200" spans="17:17">
       <c r="Q200" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="201" spans="17:17">
       <c r="Q201" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="202" spans="17:17">
       <c r="Q202" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="203" spans="17:17">
       <c r="Q203" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="204" spans="17:17">
       <c r="Q204" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="205" spans="17:17">
       <c r="Q205" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="206" spans="17:17">
       <c r="Q206" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="207" spans="17:17">
       <c r="Q207" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="208" spans="17:17">
       <c r="Q208" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="209" spans="17:17">
       <c r="Q209" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="210" spans="17:17">
       <c r="Q210" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="211" spans="17:17">
       <c r="Q211" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="212" spans="17:17">
       <c r="Q212" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" spans="17:17">
       <c r="Q213" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="214" spans="17:17">
       <c r="Q214" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="215" spans="17:17">
       <c r="Q215" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="216" spans="17:17">
       <c r="Q216" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="217" spans="17:17">
       <c r="Q217" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="218" spans="17:17">
       <c r="Q218" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="219" spans="17:17">
       <c r="Q219" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="220" spans="17:17">
       <c r="Q220" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="221" spans="17:17">
       <c r="Q221" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="222" spans="17:17">
       <c r="Q222" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="223" spans="17:17">
       <c r="Q223" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="224" spans="17:17">
       <c r="Q224" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="225" spans="17:17">
       <c r="Q225" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="226" spans="17:17">
       <c r="Q226" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="227" spans="17:17">
       <c r="Q227" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" spans="17:17">
       <c r="Q228" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="229" spans="17:17">
       <c r="Q229" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="230" spans="17:17">
       <c r="Q230" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="231" spans="17:17">
       <c r="Q231" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="232" spans="17:17">
       <c r="Q232" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="233" spans="17:17">
       <c r="Q233" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="234" spans="17:17">
       <c r="Q234" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="235" spans="17:17">
       <c r="Q235" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="236" spans="17:17">
       <c r="Q236" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="237" spans="17:17">
       <c r="Q237" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="238" spans="17:17">
       <c r="Q238" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="239" spans="17:17">
       <c r="Q239" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="240" spans="17:17">
       <c r="Q240" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="241" spans="17:17">
       <c r="Q241" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="242" spans="17:17">
       <c r="Q242" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="243" spans="17:17">
       <c r="Q243" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="244" spans="17:17">
       <c r="Q244" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="245" spans="17:17">
       <c r="Q245" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="246" spans="17:17">
       <c r="Q246" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="247" spans="17:17">
       <c r="Q247" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="248" spans="17:17">
       <c r="Q248" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="249" spans="17:17">
       <c r="Q249" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="250" spans="17:17">
       <c r="Q250" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="251" spans="17:17">
       <c r="Q251" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="252" spans="17:17">
       <c r="Q252" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="253" spans="17:17">
       <c r="Q253" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="254" spans="17:17">
       <c r="Q254" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="255" spans="17:17">
       <c r="Q255" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="256" spans="17:17">
       <c r="Q256" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="257" spans="17:17">
       <c r="Q257" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="258" spans="17:17">
       <c r="Q258" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="259" spans="17:17">
       <c r="Q259" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="260" spans="17:17">
       <c r="Q260" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="261" spans="17:17">
       <c r="Q261" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="262" spans="17:17">
       <c r="Q262" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="263" spans="17:17">
       <c r="Q263" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="264" spans="17:17">
       <c r="Q264" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="265" spans="17:17">
       <c r="Q265" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="266" spans="17:17">
       <c r="Q266" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="267" spans="17:17">
       <c r="Q267" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="268" spans="17:17">
       <c r="Q268" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="269" spans="17:17">
       <c r="Q269" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="270" spans="17:17">
       <c r="Q270" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="271" spans="17:17">
       <c r="Q271" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="272" spans="17:17">
       <c r="Q272" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="273" spans="17:17">
       <c r="Q273" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="274" spans="17:17">
       <c r="Q274" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="275" spans="17:17">
       <c r="Q275" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="276" spans="17:17">
       <c r="Q276" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="277" spans="17:17">
       <c r="Q277" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="278" spans="17:17">
       <c r="Q278" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="279" spans="17:17">
       <c r="Q279" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="280" spans="17:17">
       <c r="Q280" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="281" spans="17:17">
       <c r="Q281" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="282" spans="17:17">
       <c r="Q282" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="283" spans="17:17">
       <c r="Q283" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="284" spans="17:17">
       <c r="Q284" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="285" spans="17:17">
       <c r="Q285" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="286" spans="17:17">
       <c r="Q286" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="287" spans="17:17">
       <c r="Q287" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="288" spans="17:17">
       <c r="Q288" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="289" spans="17:17">
       <c r="Q289" t="s">
-        <v>581</v>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="290" spans="17:17">
+      <c r="Q290" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="291" spans="17:17">
+      <c r="Q291" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="292" spans="17:17">
+      <c r="Q292" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="293" spans="17:17">
+      <c r="Q293" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="294" spans="17:17">
+      <c r="Q294" t="s">
+        <v>587</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000052/metadata_template_ERC000052.xlsx
+++ b/templates/ERC000052/metadata_template_ERC000052.xlsx
@@ -1855,7 +1855,7 @@
     <t>host length</t>
   </si>
   <si>
-    <t>(Optional) The length of subject (Units: mm)</t>
+    <t>(Optional) The length of subject (Units: m)</t>
   </si>
   <si>
     <t>host total mass</t>
@@ -1939,7 +1939,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Mandatory) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Mandatory) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
